--- a/2 - AutoMax_300_Registros_Dicionario.xlsx
+++ b/2 - AutoMax_300_Registros_Dicionario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Documentos\GitHub\AUTOMAX\ProjetoIntegrador\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C9DDD185-0E04-499D-9D69-66556307F7F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4C181A-DC84-435F-910D-A94BE2BFE0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" xr2:uid="{7FAEE298-73E4-4F1E-A279-4DB220985B56}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{7FAEE298-73E4-4F1E-A279-4DB220985B56}"/>
   </bookViews>
   <sheets>
     <sheet name="2 - AutoMax_300_Registros" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="129">
   <si>
     <t>Marca</t>
   </si>
@@ -1015,7 +1015,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1027,9 +1033,6 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1039,26 +1042,23 @@
     <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1453,28 +1453,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
       <c r="G1" t="s">
         <v>126</v>
       </c>
       <c r="J1" t="s">
         <v>126</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1629,68 +1629,68 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="K6" s="8" t="s">
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="K6" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="K7" s="8" t="s">
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="K7" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="K8" s="8" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="K8" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
       <c r="G10" t="s">
         <v>126</v>
       </c>
@@ -1717,14 +1717,14 @@
       <c r="J11" t="s">
         <v>126</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="14"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
@@ -1841,14 +1841,14 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
       <c r="K15" s="2" t="s">
         <v>31</v>
       </c>
@@ -1869,14 +1869,14 @@
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
       <c r="K16" s="2" t="s">
         <v>64</v>
       </c>
@@ -1897,62 +1897,62 @@
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="K17" s="9" t="s">
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="K17" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="12"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="K18" s="8" t="s">
+      <c r="K18" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="K19" s="9" t="s">
+      <c r="K19" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="12"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="K20" s="12" t="s">
+      <c r="K20" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="14"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="6"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
       <c r="G21" t="s">
         <v>126</v>
       </c>
@@ -2019,14 +2019,14 @@
       <c r="J24" t="s">
         <v>126</v>
       </c>
-      <c r="K24" s="4" t="s">
+      <c r="K24" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
@@ -2105,14 +2105,14 @@
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="12"/>
       <c r="K27" s="2" t="s">
         <v>38</v>
       </c>
@@ -2133,14 +2133,14 @@
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
       <c r="K28" s="2" t="s">
         <v>39</v>
       </c>
@@ -2161,14 +2161,14 @@
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="12"/>
       <c r="K29" s="2" t="s">
         <v>117</v>
       </c>
@@ -2189,14 +2189,14 @@
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="14"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="6"/>
       <c r="K30" s="2" t="s">
         <v>64</v>
       </c>
@@ -2217,35 +2217,35 @@
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="K31" s="12" t="s">
+      <c r="K31" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="13"/>
-      <c r="P31" s="14"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="6"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
       <c r="G32" t="s">
         <v>126</v>
       </c>
-      <c r="K32" s="12" t="s">
+      <c r="K32" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="L32" s="13"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="13"/>
-      <c r="P32" s="14"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="6"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
@@ -2328,35 +2328,35 @@
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="14"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="6"/>
       <c r="J37" t="s">
         <v>126</v>
       </c>
-      <c r="K37" s="4" t="s">
+      <c r="K37" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+      <c r="O37" s="14"/>
+      <c r="P37" s="14"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="14"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="6"/>
       <c r="K38" s="2" t="s">
         <v>2</v>
       </c>
@@ -2397,14 +2397,17 @@
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" t="s">
+        <v>126</v>
+      </c>
       <c r="K40" s="2" t="s">
         <v>48</v>
       </c>
@@ -2482,14 +2485,14 @@
         <v>13</v>
       </c>
       <c r="J42" s="1"/>
-      <c r="K42" s="12" t="s">
+      <c r="K42" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="L42" s="13"/>
-      <c r="M42" s="13"/>
-      <c r="N42" s="13"/>
-      <c r="O42" s="13"/>
-      <c r="P42" s="14"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="6"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
@@ -2510,14 +2513,14 @@
       <c r="F43" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K43" s="12" t="s">
+      <c r="K43" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="L43" s="13"/>
-      <c r="M43" s="13"/>
-      <c r="N43" s="13"/>
-      <c r="O43" s="13"/>
-      <c r="P43" s="14"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="6"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
@@ -2601,24 +2604,24 @@
       <c r="J47" t="s">
         <v>126</v>
       </c>
-      <c r="K47" s="5" t="s">
+      <c r="K47" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="L47" s="6"/>
-      <c r="M47" s="6"/>
-      <c r="N47" s="6"/>
-      <c r="O47" s="6"/>
-      <c r="P47" s="7"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="8"/>
+      <c r="N47" s="8"/>
+      <c r="O47" s="8"/>
+      <c r="P47" s="9"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A48" s="9" t="s">
+      <c r="A48" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="11"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="12"/>
       <c r="K48" s="2" t="s">
         <v>2</v>
       </c>
@@ -2639,14 +2642,14 @@
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="11"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="12"/>
       <c r="K49" s="2" t="s">
         <v>60</v>
       </c>
@@ -2687,14 +2690,17 @@
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" t="s">
+        <v>126</v>
+      </c>
       <c r="K51" s="2" t="s">
         <v>62</v>
       </c>
@@ -2733,14 +2739,14 @@
       <c r="F52" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K52" s="12" t="s">
+      <c r="K52" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="L52" s="13"/>
-      <c r="M52" s="13"/>
-      <c r="N52" s="13"/>
-      <c r="O52" s="13"/>
-      <c r="P52" s="14"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="6"/>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
@@ -2761,14 +2767,14 @@
       <c r="F53" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K53" s="12" t="s">
+      <c r="K53" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="L53" s="13"/>
-      <c r="M53" s="13"/>
-      <c r="N53" s="13"/>
-      <c r="O53" s="13"/>
-      <c r="P53" s="14"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="6"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
@@ -2818,14 +2824,14 @@
       <c r="J55" t="s">
         <v>126</v>
       </c>
-      <c r="K55" s="5" t="s">
+      <c r="K55" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="L55" s="6"/>
-      <c r="M55" s="6"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="7"/>
+      <c r="L55" s="8"/>
+      <c r="M55" s="8"/>
+      <c r="N55" s="8"/>
+      <c r="O55" s="8"/>
+      <c r="P55" s="9"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
@@ -2998,14 +3004,14 @@
       <c r="F60" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="K60" s="12" t="s">
+      <c r="K60" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="L60" s="13"/>
-      <c r="M60" s="13"/>
-      <c r="N60" s="13"/>
-      <c r="O60" s="13"/>
-      <c r="P60" s="14"/>
+      <c r="L60" s="5"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="6"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
@@ -3026,47 +3032,47 @@
       <c r="F61" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="K61" s="12" t="s">
+      <c r="K61" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="L61" s="13"/>
-      <c r="M61" s="13"/>
-      <c r="N61" s="13"/>
-      <c r="O61" s="13"/>
-      <c r="P61" s="14"/>
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="6"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A62" s="9" t="s">
+      <c r="A62" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="B62" s="10"/>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="11"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="12"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A63" s="9" t="s">
+      <c r="A63" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B63" s="10"/>
-      <c r="C63" s="10"/>
-      <c r="D63" s="10"/>
-      <c r="E63" s="10"/>
-      <c r="F63" s="11"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="12"/>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="J64" t="s">
         <v>126</v>
       </c>
-      <c r="K64" s="5" t="s">
+      <c r="K64" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="L64" s="6"/>
-      <c r="M64" s="6"/>
-      <c r="N64" s="6"/>
-      <c r="O64" s="6"/>
-      <c r="P64" s="7"/>
+      <c r="L64" s="8"/>
+      <c r="M64" s="8"/>
+      <c r="N64" s="8"/>
+      <c r="O64" s="8"/>
+      <c r="P64" s="9"/>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="K65" s="2" t="s">
@@ -3089,14 +3095,17 @@
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A66" s="5" t="s">
+      <c r="A66" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="7"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="9"/>
+      <c r="G66" t="s">
+        <v>126</v>
+      </c>
       <c r="K66" s="2" t="s">
         <v>122</v>
       </c>
@@ -3211,14 +3220,14 @@
       <c r="F69" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="K69" s="12" t="s">
+      <c r="K69" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="L69" s="13"/>
-      <c r="M69" s="13"/>
-      <c r="N69" s="13"/>
-      <c r="O69" s="13"/>
-      <c r="P69" s="14"/>
+      <c r="L69" s="5"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="6"/>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
@@ -3239,14 +3248,14 @@
       <c r="F70" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K70" s="12" t="s">
+      <c r="K70" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="L70" s="13"/>
-      <c r="M70" s="13"/>
-      <c r="N70" s="13"/>
-      <c r="O70" s="13"/>
-      <c r="P70" s="14"/>
+      <c r="L70" s="5"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="6"/>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
@@ -3309,44 +3318,44 @@
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A74" s="9" t="s">
+      <c r="A74" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B74" s="10"/>
-      <c r="C74" s="10"/>
-      <c r="D74" s="10"/>
-      <c r="E74" s="10"/>
-      <c r="F74" s="11"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="12"/>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A75" s="9" t="s">
+      <c r="A75" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B75" s="10"/>
-      <c r="C75" s="10"/>
-      <c r="D75" s="10"/>
-      <c r="E75" s="10"/>
-      <c r="F75" s="11"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="12"/>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A76" s="12" t="s">
+      <c r="A76" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B76" s="13"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="14"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="6"/>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A77" s="15" t="s">
+      <c r="A77" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B77" s="15"/>
-      <c r="C77" s="15"/>
-      <c r="D77" s="15"/>
-      <c r="E77" s="15"/>
-      <c r="F77" s="15"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="13"/>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" s="16" t="s">
@@ -3359,21 +3368,28 @@
       <c r="F78" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="51">
-    <mergeCell ref="K61:P61"/>
-    <mergeCell ref="K64:P64"/>
-    <mergeCell ref="K69:P69"/>
-    <mergeCell ref="K70:P70"/>
-    <mergeCell ref="K42:P42"/>
-    <mergeCell ref="K47:P47"/>
-    <mergeCell ref="K55:P55"/>
-    <mergeCell ref="K19:P19"/>
-    <mergeCell ref="K31:P31"/>
-    <mergeCell ref="K32:P32"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="K43:P43"/>
-    <mergeCell ref="K52:P52"/>
+  <mergeCells count="52">
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="K18:P18"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="K1:P1"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="K7:P7"/>
+    <mergeCell ref="K8:P8"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="K11:P11"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="K37:P37"/>
+    <mergeCell ref="K24:P24"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A74:F74"/>
     <mergeCell ref="A75:F75"/>
     <mergeCell ref="A76:F76"/>
@@ -3390,27 +3406,21 @@
     <mergeCell ref="K60:P60"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="K37:P37"/>
-    <mergeCell ref="K24:P24"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="K19:P19"/>
+    <mergeCell ref="K31:P31"/>
+    <mergeCell ref="K32:P32"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="K20:P20"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="K11:P11"/>
-    <mergeCell ref="K18:P18"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="K1:P1"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="K7:P7"/>
-    <mergeCell ref="K8:P8"/>
+    <mergeCell ref="K61:P61"/>
+    <mergeCell ref="K64:P64"/>
+    <mergeCell ref="K69:P69"/>
+    <mergeCell ref="K70:P70"/>
+    <mergeCell ref="K42:P42"/>
+    <mergeCell ref="K47:P47"/>
+    <mergeCell ref="K55:P55"/>
+    <mergeCell ref="K43:P43"/>
+    <mergeCell ref="K52:P52"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <legacyDrawing r:id="rId1"/>
